--- a/classeur/FALCON.xlsx
+++ b/classeur/FALCON.xlsx
@@ -4241,19 +4241,19 @@
     </row>
   </sheetData>
   <dataValidations count="5">
-    <dataValidation sqref="C3:C500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valeur hors liste" error="Ce que l'etape fait. `set` ecrit, `press` clique, `vkey` envoie une touche de fonction, `lire` releve une valeur." promptTitle="Choisir" prompt="Ce que l'etape fait. `set` ecrit, `press` clique, `vkey` envoie une touche de fonction, `lire` releve une valeur." type="list">
+    <dataValidation sqref="C3:C500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Ce que l'etape fait. `set` ecrit, `press` clique, `vkey` envoie une touche de fonction, `lire` releve une valeur." promptTitle="Choisir" prompt="Ce que l'etape fait. `set` ecrit, `press` clique, `vkey` envoie une touche de fonction, `lire` releve une valeur." type="list">
       <formula1>"cocher,lire,press,python,select,set,vkey"</formula1>
     </dataValidation>
-    <dataValidation sqref="F3:F500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valeur hors liste" error="D'ou vient la valeur. `colonne` : du jeu. `constante` : ecrite ici, ENTRE CROCHETS. `gabarit` : composee, « /BCP01_{site} ». `lue` : le nom d'une etape `lire` precedente." promptTitle="Choisir" prompt="D'ou vient la valeur. `colonne` : du jeu. `constante` : ecrite ici, ENTRE CROCHETS. `gabarit` : composee, « /BCP01_{site} ». `lue` : le nom d'une etape `lire` precedente." type="list">
+    <dataValidation sqref="F3:F500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="D'ou vient la valeur. `colonne` : du jeu. `constante` : ecrite ici, ENTRE CROCHETS. `gabarit` : composee, « /BCP01_{site} ». `lue` : le nom d'une etape `lire` precedente." promptTitle="Choisir" prompt="D'ou vient la valeur. `colonne` : du jeu. `constante` : ecrite ici, ENTRE CROCHETS. `gabarit` : composee, « /BCP01_{site} ». `lue` : le nom d'une etape `lire` precedente." type="list">
       <formula1>"colonne,constante,gabarit,lue"</formula1>
     </dataValidation>
-    <dataValidation sqref="K3:K500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valeur hors liste" error="« oui » si cette etape VALIDE dans SAP. Pas VRAI/FAUX : le booleen d'Excel est localise et ne se relit pas d'une machine a l'autre." promptTitle="Choisir" prompt="« oui » si cette etape VALIDE dans SAP. Pas VRAI/FAUX : le booleen d'Excel est localise et ne se relit pas d'une machine a l'autre." type="list">
+    <dataValidation sqref="K3:K500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="« oui » si cette etape VALIDE dans SAP. Pas VRAI/FAUX : le booleen d'Excel est localise et ne se relit pas d'une machine a l'autre." promptTitle="Choisir" prompt="« oui » si cette etape VALIDE dans SAP. Pas VRAI/FAUX : le booleen d'Excel est localise et ne se relit pas d'une machine a l'autre." type="list">
       <formula1>"oui,non"</formula1>
     </dataValidation>
-    <dataValidation sqref="L3:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valeur hors liste" error="Comment la garde de relecture compare ce qui a ete tape a ce que SAP rend. Vide = `casse`." promptTitle="Choisir" prompt="Comment la garde de relecture compare ce qui a ete tape a ce que SAP rend. Vide = `casse`." type="list">
+    <dataValidation sqref="L3:L500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Comment la garde de relecture compare ce qui a ete tape a ce que SAP rend. Vide = `casse`." promptTitle="Choisir" prompt="Comment la garde de relecture compare ce qui a ete tape a ce que SAP rend. Vide = `casse`." type="list">
       <formula1>"casse,exact,prefixe"</formula1>
     </dataValidation>
-    <dataValidation sqref="H3:H500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valeur hors liste" error="Transformations appliquees DANS L'ORDRE, separees par des virgules. « zeros » et « tronque » prennent une largeur : « zeros:18 »." promptTitle="Choisir" prompt="Transformations appliquees DANS L'ORDRE, separees par des virgules. « zeros » et « tronque » prennent une largeur : « zeros:18 »." type="list">
+    <dataValidation sqref="H3:H500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Transformations appliquees DANS L'ORDRE, separees par des virgules. « zeros » et « tronque » prennent une largeur : « zeros:18 »." promptTitle="Choisir" prompt="Transformations appliquees DANS L'ORDRE, separees par des virgules. « zeros » et « tronque » prennent une largeur : « zeros:18 »." type="list">
       <formula1>"majuscules,minuscules,sans_espaces_autour,tronque,zeros"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4619,7 +4619,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="B3:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valeur hors liste" error="Seules ces trois gardes se derogent. Une identite violee signale que le modele du monde est faux, et le plafond est la derniere barriere." promptTitle="Choisir" prompt="Seules ces trois gardes se derogent. Une identite violee signale que le modele du monde est faux, et le plafond est la derniere barriere." type="list">
+    <dataValidation sqref="B3:B500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Seules ces trois gardes se derogent. Une identite violee signale que le modele du monde est faux, et le plafond est la derniere barriere." promptTitle="Choisir" prompt="Seules ces trois gardes se derogent. Une identite violee signale que le modele du monde est faux, et le plafond est la derniere barriere." type="list">
       <formula1>"fenetre,relecture,statut"</formula1>
     </dataValidation>
   </dataValidations>

--- a/classeur/FALCON.xlsx
+++ b/classeur/FALCON.xlsx
@@ -655,7 +655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N500"/>
+  <dimension ref="A1:P500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -672,6 +672,8 @@
     <col width="19" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -752,6 +754,16 @@
           <t>fonction</t>
         </is>
       </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>colonne</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>colonnes</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="D3" s="3" t="n"/>
@@ -4242,7 +4254,7 @@
   </sheetData>
   <dataValidations count="5">
     <dataValidation sqref="C3:C500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Ce que l'etape fait. `set` ecrit, `press` clique, `vkey` envoie une touche de fonction, `lire` releve une valeur." promptTitle="Choisir" prompt="Ce que l'etape fait. `set` ecrit, `press` clique, `vkey` envoie une touche de fonction, `lire` releve une valeur." type="list">
-      <formula1>"cocher,lire,press,python,select,set,vkey"</formula1>
+      <formula1>"choisir,cocher,extraire,lire,ouvrir,press,python,select,set,vkey"</formula1>
     </dataValidation>
     <dataValidation sqref="F3:F500" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="D'ou vient la valeur. `colonne` : du jeu. `constante` : ecrite ici, ENTRE CROCHETS. `gabarit` : composee, « /BCP01_{site} ». `lue` : le nom d'une etape `lire` precedente." promptTitle="Choisir" prompt="D'ou vient la valeur. `colonne` : du jeu. `constante` : ecrite ici, ENTRE CROCHETS. `gabarit` : composee, « /BCP01_{site} ». `lue` : le nom d'une etape `lire` precedente." type="list">
       <formula1>"colonne,constante,gabarit,lue"</formula1>
@@ -4267,7 +4279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4284,6 +4296,8 @@
     <col width="19" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4364,6 +4378,16 @@
           <t>fonction</t>
         </is>
       </c>
+      <c r="O2" s="6" t="inlineStr">
+        <is>
+          <t>colonne</t>
+        </is>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>colonnes</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
